--- a/reports/bandeirante/perfil_estatistico_anual.xlsx
+++ b/reports/bandeirante/perfil_estatistico_anual.xlsx
@@ -9256,7 +9256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9553,6 +9553,23 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>regra</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sem as Taxas TEIFa Oper e TEIP Oper no nível da usina</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/bandeirante/perfil_estatistico_anual.xlsx
+++ b/reports/bandeirante/perfil_estatistico_anual.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Série de referência: Geração por usina do conjunto Conj. Chapadão (id ONS CJU_MSCAO), de 22/08/2019 00h a 20/10/2026 23h: 62.064 horas com registro de 62.808 no período (98,82%). 744 horas ausentes, listadas na planilha, sem preenchimento. O período tem 3 trechos, com mudança de modalidade, de composição do conjunto ou de código.</t>
+          <t>Série de referência: Geração por usina do conjunto Conj. Chapadão (id ONS CJU_MSCAO), de 22/08/2019 00h a 27/10/2026 23h: 62.232 horas com registro de 62.976 no período (98,82%). 744 horas ausentes, listadas na planilha, sem preenchimento. O período tem 3 trechos, com mudança de modalidade, de composição do conjunto ou de código.</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O ONS publica a geração, a programação e os demais dados de operação do conjunto Conj. Chapadão (CJU_MSCAO), e não os da PCH Bandeirante isolada. Peso da usina (28,0 MW) na potência das usinas do conjunto: 6,7% de 27/09/2019 a 30/06/2025 e 35,7% de 01/07/2025 a 20/10/2026; esse peso não estima a geração dela.</t>
+          <t>O ONS publica a geração, a programação e os demais dados de operação do conjunto Conj. Chapadão (CJU_MSCAO), e não os da PCH Bandeirante isolada. Peso da usina (28,0 MW) na potência das usinas do conjunto: 6,7% de 27/09/2019 a 30/06/2025 e 35,7% de 01/07/2025 a 27/10/2026; esse peso não estima a geração dela.</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geração média do conjunto Conj. Chapadão de 115,0 MWmed nas 62.064 horas com valor (7.135.437 MWh); geração até 1 MW em 0,0% das horas; entre os anos completos, maior média em 2020 (134,5 MWmed) e menor em 2025 (71,8 MWmed).</t>
+          <t>Geração média do conjunto Conj. Chapadão de 114,7 MWmed nas 62.232 horas com valor (7.140.552 MWh); geração até 1 MW em 0,0% das horas; entre os anos completos, maior média em 2020 (134,5 MWmed) e menor em 2025 (71,8 MWmed).</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nas 17.472 horas com programação e geração verificada do conjunto Conj. Chapadão, geração verificada média de 70,0 MW e programada de 69,3 MW (desvio médio absoluto de 10,8 MW; correlação de 0,92); 0 horas com geração até 1 MW e programação acima de 5 MW.</t>
+          <t>Nas 17.640 horas com programação e geração verificada do conjunto Conj. Chapadão, geração verificada média de 69,6 MW e programada de 68,9 MW (desvio médio absoluto de 10,7 MW; correlação de 0,92); 0 horas com geração até 1 MW e programação acima de 5 MW.</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O conjunto Conj. Chapadão (CJU_MSCAO) teve 3 composições no período: de 22/08/2019 a 26/09/2019, 8 usinas (PCH e UTE), geração média do conjunto de 167,6 MWmed; de 27/09/2019 a 30/06/2025, 9 usinas (PCH e UTE), geração média do conjunto de 129,7 MWmed; de 01/07/2025 a 20/10/2026, 4 usinas (PCH), geração média do conjunto de 47,0 MWmed. Os números são do conjunto, sem divisão entre as usinas.</t>
+          <t>O conjunto Conj. Chapadão (CJU_MSCAO) teve 3 composições no período: de 22/08/2019 a 26/09/2019, 8 usinas (PCH e UTE), geração média do conjunto de 167,6 MWmed; de 27/09/2019 a 30/06/2025, 9 usinas (PCH e UTE), geração média do conjunto de 129,7 MWmed; de 01/07/2025 a 27/10/2026, 4 usinas (PCH), geração média do conjunto de 46,8 MWmed. Os números são do conjunto, sem divisão entre as usinas.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nenhuma hora sinalizada na base horária. A Geração por usina traz 4.152 linhas próprias da usina sem valor, de 01/05/2026 a 20/10/2026; a série usada é a do conjunto. O ONS publica a série do conjunto como TÉRMICA (Biomassa) de 01/07/2025 a 20/10/2026, quando a composição tem só PCH; o tipo das usinas vem do CEG.</t>
+          <t>Nenhuma hora sinalizada na base horária. A Geração por usina traz 4.320 linhas próprias da usina sem valor, de 01/05/2026 a 27/10/2026; a série usada é a do conjunto. O ONS publica a série do conjunto como TÉRMICA (Biomassa) de 01/07/2025 a 27/10/2026, quando a composição tem só PCH; o tipo das usinas vem do CEG.</t>
         </is>
       </c>
     </row>
@@ -1678,19 +1678,19 @@
         <v>46296</v>
       </c>
       <c r="B26" t="n">
-        <v>480</v>
+        <v>648</v>
       </c>
       <c r="C26" t="n">
-        <v>33.70705874010341</v>
+        <v>32.86223330532388</v>
       </c>
       <c r="D26" t="n">
-        <v>30.20833333333333</v>
+        <v>30.74691358024691</v>
       </c>
       <c r="E26" t="n">
-        <v>3.498725406770077</v>
+        <v>2.115319725076971</v>
       </c>
       <c r="F26" t="n">
-        <v>7.737308608852327</v>
+        <v>6.962767845555956</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>45839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -1885,16 +1885,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11448</v>
+        <v>11616</v>
       </c>
       <c r="G4" t="n">
-        <v>11448</v>
+        <v>11616</v>
       </c>
       <c r="H4" t="n">
-        <v>538110.3132620552</v>
+        <v>543225.6522486554</v>
       </c>
       <c r="I4" t="n">
-        <v>47.00474434504326</v>
+        <v>46.76529375418865</v>
       </c>
       <c r="J4" t="n">
         <v>184.294</v>
@@ -4198,13 +4198,13 @@
         <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>480</v>
+        <v>648</v>
       </c>
       <c r="D88" t="n">
-        <v>33.70705874010341</v>
+        <v>32.86223330532388</v>
       </c>
       <c r="E88" t="n">
-        <v>16179.38819524964</v>
+        <v>21294.72718184988</v>
       </c>
     </row>
   </sheetData>
@@ -4345,7 +4345,7 @@
         <v>45839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11448</v>
+        <v>11616</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="D4" t="n">
         <v>27.9999</v>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:15</t>
+          <t>2026-10-29 14:16:36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6025</v>
+        <v>6048</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:18</t>
+          <t>2026-10-29 15:00:41</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:18</t>
+          <t>2026-10-29 15:00:41</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:24</t>
+          <t>2026-10-29 15:00:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:24</t>
+          <t>2026-10-29 15:00:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:27</t>
+          <t>2026-10-29 15:00:48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:27</t>
+          <t>2026-10-29 15:00:48</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:30</t>
+          <t>2026-10-29 15:00:50</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:30</t>
+          <t>2026-10-29 15:00:50</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:34</t>
+          <t>2026-10-29 15:00:53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:34</t>
+          <t>2026-10-29 15:00:53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 20/10/2026; Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Capacidade de geração (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 29/10/2026; Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Capacidade de geração (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 20/10/2026; Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Capacidade de geração (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 29/10/2026; Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Capacidade de geração (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 20/10/2026; Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Capacidade de geração (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 29/10/2026; Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Capacidade de geração (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 29/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 22/10/2026</t>
+          <t>Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MSCAO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026</t>
+          <t>Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026</t>
+          <t>Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 22/10/2026; Capacidade de geração (CEG PCH.PH.MS.032163-0.01), obtido em 22/10/2026</t>
+          <t>Programação diária (conjunto de usinas, MSCAO-9761; MSCAO-9762; MSCAO-9763; MSCAO-9766; MSCAO-10205; MSCAO-9764; MSCAO-9765; MSCAO-9784), obtido em 29/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Modalidade das usinas (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MSCAO), obtido em 29/10/2026; Capacidade de geração (CEG PCH.PH.MS.032163-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6335,16 +6335,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>7032</v>
+        <v>7200</v>
       </c>
       <c r="E9" t="n">
-        <v>7032</v>
+        <v>7200</v>
       </c>
       <c r="F9" t="n">
-        <v>51.00607953100899</v>
+        <v>50.52640142342437</v>
       </c>
       <c r="G9" t="n">
-        <v>358674.7512620552</v>
+        <v>363790.0902486555</v>
       </c>
       <c r="H9" t="n">
         <v>73.94499999999999</v>
@@ -8293,16 +8293,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>480</v>
+        <v>648</v>
       </c>
       <c r="D87" t="n">
-        <v>480</v>
+        <v>648</v>
       </c>
       <c r="E87" t="n">
-        <v>33.70705874010341</v>
+        <v>32.86223330532388</v>
       </c>
       <c r="F87" t="n">
-        <v>16179.38819524964</v>
+        <v>21294.72718184988</v>
       </c>
     </row>
   </sheetData>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>123.1953629035699</v>
+        <v>120.1473421717234</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.2841187454339</v>
+        <v>116.0506070776942</v>
       </c>
       <c r="D2" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="3">
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115.9912525489175</v>
+        <v>115.7585117643382</v>
       </c>
       <c r="D3" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="4">
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115.9966425249431</v>
+        <v>115.7638518969572</v>
       </c>
       <c r="D4" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="5">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116.0645040198191</v>
+        <v>115.8287667031276</v>
       </c>
       <c r="D5" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="6">
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>115.8241904160553</v>
+        <v>115.5894852941428</v>
       </c>
       <c r="D6" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="7">
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>115.7799153672969</v>
+        <v>115.5460068203543</v>
       </c>
       <c r="D7" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="8">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>115.7005461212842</v>
+        <v>115.4667953457184</v>
       </c>
       <c r="D8" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="9">
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>115.2570131818833</v>
+        <v>115.0251679308582</v>
       </c>
       <c r="D9" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="10">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>114.3941974851906</v>
+        <v>114.1661560213759</v>
       </c>
       <c r="D10" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="11">
@@ -8735,10 +8735,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>113.3206641137963</v>
+        <v>113.0950007098935</v>
       </c>
       <c r="D11" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="12">
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>112.8275777849033</v>
+        <v>112.6034939205994</v>
       </c>
       <c r="D12" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="13">
@@ -8767,10 +8767,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>112.4772393988524</v>
+        <v>112.2531664271419</v>
       </c>
       <c r="D13" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="14">
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>112.420889284991</v>
+        <v>112.1972961081542</v>
       </c>
       <c r="D14" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="15">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>112.6533463505529</v>
+        <v>112.4267439149349</v>
       </c>
       <c r="D15" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="16">
@@ -8815,10 +8815,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>112.617755205101</v>
+        <v>112.390819875841</v>
       </c>
       <c r="D16" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="17">
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>112.612215244171</v>
+        <v>112.3896542428372</v>
       </c>
       <c r="D17" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="18">
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>113.135277729774</v>
+        <v>112.9122410145611</v>
       </c>
       <c r="D18" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="19">
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>114.3887183093126</v>
+        <v>114.1640724015184</v>
       </c>
       <c r="D19" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="20">
@@ -8879,10 +8879,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>115.9844046855171</v>
+        <v>115.7591457495246</v>
       </c>
       <c r="D20" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="21">
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>116.9301042537997</v>
+        <v>116.7082341431729</v>
       </c>
       <c r="D21" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="22">
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>117.4390285533814</v>
+        <v>117.2150298448323</v>
       </c>
       <c r="D22" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="23">
@@ -8927,10 +8927,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>117.299959442171</v>
+        <v>117.0761362257676</v>
       </c>
       <c r="D23" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="24">
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>117.0695801611922</v>
+        <v>116.8404867523382</v>
       </c>
       <c r="D24" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="25">
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>116.7871120732284</v>
+        <v>116.5533107817881</v>
       </c>
       <c r="D25" t="n">
-        <v>2586</v>
+        <v>2593</v>
       </c>
     </row>
   </sheetData>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-20 23:00:00</t>
+          <t>2026-10-27 23:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
